--- a/final_data_pipeline/output/311423_elec_options.xlsx
+++ b/final_data_pipeline/output/311423_elec_options.xlsx
@@ -5058,7 +5058,7 @@
         <v>57</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5147,7 +5147,7 @@
         <v>57</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5236,7 +5236,7 @@
         <v>57</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5325,7 +5325,7 @@
         <v>57</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5414,7 +5414,7 @@
         <v>57</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5503,7 +5503,7 @@
         <v>57</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6126,7 +6126,7 @@
         <v>57</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6215,7 +6215,7 @@
         <v>57</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6304,7 +6304,7 @@
         <v>57</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -6393,7 +6393,7 @@
         <v>57</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -6482,7 +6482,7 @@
         <v>57</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -6571,7 +6571,7 @@
         <v>57</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE67">
         <v>8000</v>
